--- a/main/ig/StructureDefinition-dmi-supplydelivery-transport.xlsx
+++ b/main/ig/StructureDefinition-dmi-supplydelivery-transport.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.0.0</t>
+    <t>3.0.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-27T10:37:28+00:00</t>
+    <t>2026-03-05T09:47:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-dmi-supplydelivery-transport.xlsx
+++ b/main/ig/StructureDefinition-dmi-supplydelivery-transport.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-05T09:47:44+00:00</t>
+    <t>2026-03-05T10:00:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-dmi-supplydelivery-transport.xlsx
+++ b/main/ig/StructureDefinition-dmi-supplydelivery-transport.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1039" uniqueCount="257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1047" uniqueCount="266">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-05T10:00:25+00:00</t>
+    <t>2026-03-05T10:01:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -266,7 +266,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}</t>
+dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}</t>
   </si>
   <si>
     <t>Event</t>
@@ -316,10 +316,17 @@
     <t>Resource.meta</t>
   </si>
   <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
     <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
+    <t>N/A</t>
+  </si>
+  <si>
     <t>SupplyDelivery.implicitRules</t>
   </si>
   <si>
@@ -339,6 +346,9 @@
     <t>Resource.implicitRules</t>
   </si>
   <si>
+    <t>n/a</t>
+  </si>
+  <si>
     <t>SupplyDelivery.language</t>
   </si>
   <si>
@@ -416,9 +426,6 @@
     <t>DomainResource.contained</t>
   </si>
   <si>
-    <t>N/A</t>
-  </si>
-  <si>
     <t>SupplyDelivery.extension</t>
   </si>
   <si>
@@ -436,6 +443,9 @@
 </t>
   </si>
   <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
     <t>open</t>
   </si>
   <si>
@@ -462,10 +472,6 @@
     <t>Extension créée dans ce volet pour représenter le transport.</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
     <t>SupplyDelivery.extension:ReferenceOrganisationInterne</t>
   </si>
   <si>
@@ -527,6 +533,9 @@
     <t>.id</t>
   </si>
   <si>
+    <t>CX / EI (occasionally, more often EI maps to a resource id or a URL)</t>
+  </si>
+  <si>
     <t>SupplyDelivery.basedOn</t>
   </si>
   <si>
@@ -540,7 +549,14 @@
     <t>A plan, proposal or order that is fulfilled in whole or in part by this event.</t>
   </si>
   <si>
+    <t>References SHALL be a reference to an actual FHIR resource, and SHALL be resolveable (allowing for access control, temporary unavailability, etc.). Resolution can be either by retrieval from the URL, or, where applicable by resource type, by treating an absolute reference as a canonical URL and looking it up in a local registry/repository.</t>
+  </si>
+  <si>
     <t>Allows tracing of authorization for the event and tracking whether proposals/recommendations were acted upon.</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
   </si>
   <si>
     <t>Event.basedOn</t>
@@ -641,6 +657,9 @@
     <t>Indicates the type of dispensing event that is performed. Examples include: Trial Fill, Completion of Trial, Partial Fill, Emergency Fill, Samples, etc.</t>
   </si>
   <si>
+    <t>Not all terminology uses fit this general pattern. In some cases, models should not use CodeableConcept and use Coding directly and provide their own structure for managing text, codings, translations and the relationship between elements and pre- and post-coordination.</t>
+  </si>
+  <si>
     <t>The type of supply dispense.</t>
   </si>
   <si>
@@ -651,6 +670,9 @@
   </si>
   <si>
     <t>.code</t>
+  </si>
+  <si>
+    <t>CE/CNE/CWE</t>
   </si>
   <si>
     <t>SupplyDelivery.suppliedItem</t>
@@ -685,9 +707,6 @@
     <t>Element.id</t>
   </si>
   <si>
-    <t>n/a</t>
-  </si>
-  <si>
     <t>SupplyDelivery.suppliedItem.extension</t>
   </si>
   <si>
@@ -730,7 +749,17 @@
     <t>The amount of supply that has been dispensed. Includes unit of measure.</t>
   </si>
   <si>
+    <t>The context of use may frequently define what kind of quantity this is and therefore what kind of units can be used. The context of use may also restrict the values for the comparator.</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+qty-3:If a code for the unit is present, the system SHALL also be present {code.empty() or system.exists()}sqty-1:The comparator is not used on a SimpleQuantity {comparator.empty()}</t>
+  </si>
+  <si>
     <t>.quantity</t>
+  </si>
+  <si>
+    <t>SN (see also Range) or CQ</t>
   </si>
   <si>
     <t>SupplyDelivery.suppliedItem.item[x]</t>
@@ -1152,7 +1181,7 @@
     <col min="26" max="26" width="43.90234375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="30.5546875" customWidth="true" bestFit="true" hidden="true"/>
@@ -1161,7 +1190,7 @@
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="25.4609375" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="52.23046875" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="27.45703125" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="53.91015625" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="31.65234375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
@@ -1607,16 +1636,16 @@
         <v>87</v>
       </c>
       <c r="AI4" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL4" t="s" s="2">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="AM4" t="s" s="2">
         <v>77</v>
@@ -1627,10 +1656,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -1653,16 +1682,16 @@
         <v>88</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -1712,7 +1741,7 @@
         <v>77</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>78</v>
@@ -1721,16 +1750,16 @@
         <v>87</v>
       </c>
       <c r="AI5" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL5" t="s" s="2">
-        <v>77</v>
+        <v>108</v>
       </c>
       <c r="AM5" t="s" s="2">
         <v>77</v>
@@ -1741,10 +1770,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1767,16 +1796,16 @@
         <v>77</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -1802,13 +1831,13 @@
         <v>77</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>77</v>
@@ -1826,7 +1855,7 @@
         <v>77</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>78</v>
@@ -1835,16 +1864,16 @@
         <v>87</v>
       </c>
       <c r="AI6" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL6" t="s" s="2">
-        <v>77</v>
+        <v>108</v>
       </c>
       <c r="AM6" t="s" s="2">
         <v>77</v>
@@ -1855,14 +1884,14 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
@@ -1881,16 +1910,16 @@
         <v>77</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -1940,7 +1969,7 @@
         <v>77</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>78</v>
@@ -1949,16 +1978,16 @@
         <v>87</v>
       </c>
       <c r="AI7" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL7" t="s" s="2">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="AM7" t="s" s="2">
         <v>77</v>
@@ -1969,14 +1998,14 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
@@ -1995,16 +2024,16 @@
         <v>77</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2054,7 +2083,7 @@
         <v>77</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>78</v>
@@ -2072,7 +2101,7 @@
         <v>77</v>
       </c>
       <c r="AL8" t="s" s="2">
-        <v>130</v>
+        <v>101</v>
       </c>
       <c r="AM8" t="s" s="2">
         <v>77</v>
@@ -2083,10 +2112,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -2109,13 +2138,13 @@
         <v>77</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -2154,17 +2183,19 @@
         <v>77</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="AC9" s="2"/>
+        <v>137</v>
+      </c>
+      <c r="AC9" t="s" s="2">
+        <v>138</v>
+      </c>
       <c r="AD9" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>78</v>
@@ -2173,10 +2204,10 @@
         <v>79</v>
       </c>
       <c r="AI9" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>77</v>
@@ -2193,13 +2224,13 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="D10" t="s" s="2">
         <v>77</v>
@@ -2221,13 +2252,13 @@
         <v>77</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -2278,7 +2309,7 @@
         <v>77</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>78</v>
@@ -2287,10 +2318,10 @@
         <v>79</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>144</v>
+        <v>99</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>77</v>
@@ -2307,13 +2338,13 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C11" t="s" s="2">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D11" t="s" s="2">
         <v>77</v>
@@ -2335,13 +2366,13 @@
         <v>77</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -2392,7 +2423,7 @@
         <v>77</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>78</v>
@@ -2401,10 +2432,10 @@
         <v>79</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>144</v>
+        <v>99</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="AK11" t="s" s="2">
         <v>77</v>
@@ -2421,14 +2452,14 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
@@ -2447,19 +2478,19 @@
         <v>77</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="O12" t="s" s="2">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="P12" t="s" s="2">
         <v>77</v>
@@ -2496,19 +2527,19 @@
         <v>77</v>
       </c>
       <c r="AB12" t="s" s="2">
-        <v>77</v>
+        <v>137</v>
       </c>
       <c r="AC12" t="s" s="2">
-        <v>77</v>
+        <v>138</v>
       </c>
       <c r="AD12" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE12" t="s" s="2">
-        <v>77</v>
+        <v>139</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>78</v>
@@ -2517,16 +2548,16 @@
         <v>79</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="AK12" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>130</v>
+        <v>101</v>
       </c>
       <c r="AM12" t="s" s="2">
         <v>77</v>
@@ -2537,10 +2568,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2563,16 +2594,16 @@
         <v>77</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -2622,7 +2653,7 @@
         <v>77</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>78</v>
@@ -2631,19 +2662,19 @@
         <v>79</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>77</v>
+        <v>166</v>
       </c>
       <c r="AN13" t="s" s="2">
         <v>77</v>
@@ -2651,10 +2682,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2677,17 +2708,19 @@
         <v>88</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="N14" s="2"/>
+        <v>170</v>
+      </c>
+      <c r="N14" t="s" s="2">
+        <v>171</v>
+      </c>
       <c r="O14" t="s" s="2">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>77</v>
@@ -2736,7 +2769,7 @@
         <v>77</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>78</v>
@@ -2745,19 +2778,19 @@
         <v>79</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>99</v>
+        <v>173</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="AN14" t="s" s="2">
         <v>77</v>
@@ -2765,10 +2798,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2791,19 +2824,19 @@
         <v>88</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="O15" t="s" s="2">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>77</v>
@@ -2852,7 +2885,7 @@
         <v>77</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>78</v>
@@ -2861,19 +2894,19 @@
         <v>79</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>99</v>
+        <v>173</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="AN15" t="s" s="2">
         <v>77</v>
@@ -2881,10 +2914,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2907,16 +2940,16 @@
         <v>88</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -2942,31 +2975,31 @@
         <v>77</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="Y16" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="Z16" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="AA16" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB16" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC16" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD16" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE16" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF16" t="s" s="2">
         <v>186</v>
-      </c>
-      <c r="Z16" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="AA16" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB16" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC16" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD16" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE16" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF16" t="s" s="2">
-        <v>181</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>78</v>
@@ -2975,16 +3008,16 @@
         <v>87</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>77</v>
@@ -2995,10 +3028,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3021,15 +3054,17 @@
         <v>77</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="N17" s="2"/>
+        <v>198</v>
+      </c>
+      <c r="N17" t="s" s="2">
+        <v>171</v>
+      </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>77</v>
@@ -3078,7 +3113,7 @@
         <v>77</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
@@ -3087,16 +3122,16 @@
         <v>87</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>99</v>
+        <v>173</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>77</v>
@@ -3107,10 +3142,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3133,15 +3168,17 @@
         <v>77</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="N18" s="2"/>
+        <v>204</v>
+      </c>
+      <c r="N18" t="s" s="2">
+        <v>205</v>
+      </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>77</v>
@@ -3166,31 +3203,31 @@
         <v>77</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="Z18" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="AA18" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB18" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC18" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD18" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE18" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF18" t="s" s="2">
         <v>201</v>
-      </c>
-      <c r="AA18" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB18" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC18" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD18" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE18" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF18" t="s" s="2">
-        <v>196</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -3199,19 +3236,19 @@
         <v>87</v>
       </c>
       <c r="AI18" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>77</v>
+        <v>210</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>77</v>
@@ -3219,10 +3256,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3245,13 +3282,13 @@
         <v>77</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -3302,7 +3339,7 @@
         <v>77</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -3311,16 +3348,16 @@
         <v>87</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>77</v>
@@ -3331,10 +3368,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3357,13 +3394,13 @@
         <v>77</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3414,7 +3451,7 @@
         <v>77</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
@@ -3432,7 +3469,7 @@
         <v>77</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>214</v>
+        <v>108</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>77</v>
@@ -3443,14 +3480,14 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -3469,16 +3506,16 @@
         <v>77</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -3516,19 +3553,19 @@
         <v>77</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>77</v>
+        <v>137</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>77</v>
+        <v>138</v>
       </c>
       <c r="AD21" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>77</v>
+        <v>139</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -3537,16 +3574,16 @@
         <v>79</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>214</v>
+        <v>101</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>77</v>
@@ -3557,14 +3594,14 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
@@ -3583,19 +3620,19 @@
         <v>88</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>77</v>
@@ -3644,7 +3681,7 @@
         <v>77</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -3653,16 +3690,16 @@
         <v>79</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>130</v>
+        <v>101</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>77</v>
@@ -3673,10 +3710,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3699,15 +3736,17 @@
         <v>77</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="N23" s="2"/>
+        <v>233</v>
+      </c>
+      <c r="N23" t="s" s="2">
+        <v>234</v>
+      </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>77</v>
@@ -3756,7 +3795,7 @@
         <v>77</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -3765,19 +3804,19 @@
         <v>87</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>99</v>
+        <v>235</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>77</v>
+        <v>237</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>77</v>
@@ -3785,10 +3824,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>229</v>
+        <v>238</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>229</v>
+        <v>238</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3811,13 +3850,13 @@
         <v>77</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>230</v>
+        <v>239</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3868,7 +3907,7 @@
         <v>77</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>229</v>
+        <v>238</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -3877,16 +3916,16 @@
         <v>87</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>77</v>
@@ -3897,10 +3936,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3923,16 +3962,16 @@
         <v>88</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -3982,7 +4021,7 @@
         <v>77</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -3991,30 +4030,30 @@
         <v>87</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>238</v>
+        <v>247</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>240</v>
+        <v>249</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>241</v>
+        <v>250</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>241</v>
+        <v>250</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4037,15 +4076,17 @@
         <v>77</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>242</v>
+        <v>251</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>243</v>
+        <v>252</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="N26" s="2"/>
+        <v>253</v>
+      </c>
+      <c r="N26" t="s" s="2">
+        <v>171</v>
+      </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>77</v>
@@ -4094,7 +4135,7 @@
         <v>77</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>241</v>
+        <v>250</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -4103,16 +4144,16 @@
         <v>87</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>99</v>
+        <v>173</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>77</v>
@@ -4123,10 +4164,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4149,15 +4190,17 @@
         <v>77</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>249</v>
+        <v>258</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="N27" s="2"/>
+        <v>259</v>
+      </c>
+      <c r="N27" t="s" s="2">
+        <v>171</v>
+      </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>77</v>
@@ -4206,7 +4249,7 @@
         <v>77</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -4215,16 +4258,16 @@
         <v>87</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>99</v>
+        <v>173</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>251</v>
+        <v>260</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>77</v>
@@ -4235,10 +4278,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>252</v>
+        <v>261</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>252</v>
+        <v>261</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4261,15 +4304,17 @@
         <v>77</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>253</v>
+        <v>262</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>254</v>
+        <v>263</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="N28" s="2"/>
+        <v>264</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>171</v>
+      </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>77</v>
@@ -4318,7 +4363,7 @@
         <v>77</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>252</v>
+        <v>261</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -4327,16 +4372,16 @@
         <v>79</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>99</v>
+        <v>173</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>256</v>
+        <v>265</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>77</v>

--- a/main/ig/StructureDefinition-dmi-supplydelivery-transport.xlsx
+++ b/main/ig/StructureDefinition-dmi-supplydelivery-transport.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1047" uniqueCount="266">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1039" uniqueCount="257">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-05T10:01:25+00:00</t>
+    <t>2026-03-05T10:22:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -266,7 +266,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}</t>
   </si>
   <si>
     <t>Event</t>
@@ -316,162 +316,156 @@
     <t>Resource.meta</t>
   </si>
   <si>
+    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+</t>
+  </si>
+  <si>
+    <t>SupplyDelivery.implicitRules</t>
+  </si>
+  <si>
+    <t xml:space="preserve">uri
+</t>
+  </si>
+  <si>
+    <t>A set of rules under which this content was created</t>
+  </si>
+  <si>
+    <t>A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
+  </si>
+  <si>
+    <t>Asserting this rule set restricts the content to be only understood by a limited set of trading partners. This inherently limits the usefulness of the data in the long term. However, the existing health eco-system is highly fractured, and not yet ready to define, collect, and exchange data in a generally computable sense. Wherever possible, implementers and/or specification writers should avoid using this element. Often, when used, the URL is a reference to an implementation guide that defines these special rules as part of it's narrative along with other profiles, value sets, etc.</t>
+  </si>
+  <si>
+    <t>Resource.implicitRules</t>
+  </si>
+  <si>
+    <t>SupplyDelivery.language</t>
+  </si>
+  <si>
+    <t xml:space="preserve">code
+</t>
+  </si>
+  <si>
+    <t>Language of the resource content</t>
+  </si>
+  <si>
+    <t>The base language in which the resource is written.</t>
+  </si>
+  <si>
+    <t>Language is provided to support indexing and accessibility (typically, services such as text to speech use the language tag). The html language tag in the narrative applies  to the narrative. The language tag on the resource may be used to specify the language of other presentations generated from the data in the resource. Not all the content has to be in the base language. The Resource.language should not be assumed to apply to the narrative automatically. If a language is specified, it should it also be specified on the div element in the html (see rules in HTML5 for information about the relationship between xml:lang and the html lang attribute).</t>
+  </si>
+  <si>
+    <t>preferred</t>
+  </si>
+  <si>
+    <t>A human language.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
+  </si>
+  <si>
+    <t>Resource.language</t>
+  </si>
+  <si>
+    <t>SupplyDelivery.text</t>
+  </si>
+  <si>
+    <t>narrative
+htmlxhtmldisplay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Narrative
+</t>
+  </si>
+  <si>
+    <t>Text summary of the resource, for human interpretation</t>
+  </si>
+  <si>
+    <t>A human-readable narrative that contains a summary of the resource and can be used to represent the content of the resource to a human. The narrative need not encode all the structured data, but is required to contain sufficient detail to make it "clinically safe" for a human to just read the narrative. Resource definitions may define what content should be represented in the narrative to ensure clinical safety.</t>
+  </si>
+  <si>
+    <t>Contained resources do not have narrative. Resources that are not contained SHOULD have a narrative. In some cases, a resource may only have text with little or no additional discrete data (as long as all minOccurs=1 elements are satisfied).  This may be necessary for data from legacy systems where information is captured as a "text blob" or where text is additionally entered raw or narrated and encoded information is added later.</t>
+  </si>
+  <si>
+    <t>DomainResource.text</t>
+  </si>
+  <si>
+    <t>Act.text?</t>
+  </si>
+  <si>
+    <t>SupplyDelivery.contained</t>
+  </si>
+  <si>
+    <t>inline resources
+anonymous resourcescontained resources</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Resource
+</t>
+  </si>
+  <si>
+    <t>Contained, inline Resources</t>
+  </si>
+  <si>
+    <t>These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, and nor can they have their own independent transaction scope.</t>
+  </si>
+  <si>
+    <t>This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags In their meta elements, but SHALL NOT have security labels.</t>
+  </si>
+  <si>
+    <t>DomainResource.contained</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>SupplyDelivery.extension</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension
+</t>
+  </si>
+  <si>
+    <t>Extension</t>
+  </si>
+  <si>
+    <t>An Extension</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>DomainResource.extension</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
+    <t>SupplyDelivery.extension:Transport</t>
+  </si>
+  <si>
+    <t>Transport</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/tdmi/StructureDefinition/dmi-transport}
+</t>
+  </si>
+  <si>
+    <t>DMI Transport</t>
+  </si>
+  <si>
+    <t>Extension créée dans ce volet pour représenter le transport.</t>
+  </si>
+  <si>
     <t xml:space="preserve">ele-1
 </t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-</t>
-  </si>
-  <si>
-    <t>N/A</t>
-  </si>
-  <si>
-    <t>SupplyDelivery.implicitRules</t>
-  </si>
-  <si>
-    <t xml:space="preserve">uri
-</t>
-  </si>
-  <si>
-    <t>A set of rules under which this content was created</t>
-  </si>
-  <si>
-    <t>A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
-  </si>
-  <si>
-    <t>Asserting this rule set restricts the content to be only understood by a limited set of trading partners. This inherently limits the usefulness of the data in the long term. However, the existing health eco-system is highly fractured, and not yet ready to define, collect, and exchange data in a generally computable sense. Wherever possible, implementers and/or specification writers should avoid using this element. Often, when used, the URL is a reference to an implementation guide that defines these special rules as part of it's narrative along with other profiles, value sets, etc.</t>
-  </si>
-  <si>
-    <t>Resource.implicitRules</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
-    <t>SupplyDelivery.language</t>
-  </si>
-  <si>
-    <t xml:space="preserve">code
-</t>
-  </si>
-  <si>
-    <t>Language of the resource content</t>
-  </si>
-  <si>
-    <t>The base language in which the resource is written.</t>
-  </si>
-  <si>
-    <t>Language is provided to support indexing and accessibility (typically, services such as text to speech use the language tag). The html language tag in the narrative applies  to the narrative. The language tag on the resource may be used to specify the language of other presentations generated from the data in the resource. Not all the content has to be in the base language. The Resource.language should not be assumed to apply to the narrative automatically. If a language is specified, it should it also be specified on the div element in the html (see rules in HTML5 for information about the relationship between xml:lang and the html lang attribute).</t>
-  </si>
-  <si>
-    <t>preferred</t>
-  </si>
-  <si>
-    <t>A human language.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
-  </si>
-  <si>
-    <t>Resource.language</t>
-  </si>
-  <si>
-    <t>SupplyDelivery.text</t>
-  </si>
-  <si>
-    <t>narrative
-htmlxhtmldisplay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Narrative
-</t>
-  </si>
-  <si>
-    <t>Text summary of the resource, for human interpretation</t>
-  </si>
-  <si>
-    <t>A human-readable narrative that contains a summary of the resource and can be used to represent the content of the resource to a human. The narrative need not encode all the structured data, but is required to contain sufficient detail to make it "clinically safe" for a human to just read the narrative. Resource definitions may define what content should be represented in the narrative to ensure clinical safety.</t>
-  </si>
-  <si>
-    <t>Contained resources do not have narrative. Resources that are not contained SHOULD have a narrative. In some cases, a resource may only have text with little or no additional discrete data (as long as all minOccurs=1 elements are satisfied).  This may be necessary for data from legacy systems where information is captured as a "text blob" or where text is additionally entered raw or narrated and encoded information is added later.</t>
-  </si>
-  <si>
-    <t>DomainResource.text</t>
-  </si>
-  <si>
-    <t>Act.text?</t>
-  </si>
-  <si>
-    <t>SupplyDelivery.contained</t>
-  </si>
-  <si>
-    <t>inline resources
-anonymous resourcescontained resources</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Resource
-</t>
-  </si>
-  <si>
-    <t>Contained, inline Resources</t>
-  </si>
-  <si>
-    <t>These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, and nor can they have their own independent transaction scope.</t>
-  </si>
-  <si>
-    <t>This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags In their meta elements, but SHALL NOT have security labels.</t>
-  </si>
-  <si>
-    <t>DomainResource.contained</t>
-  </si>
-  <si>
-    <t>SupplyDelivery.extension</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension
-</t>
-  </si>
-  <si>
-    <t>Extension</t>
-  </si>
-  <si>
-    <t>An Extension</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
-    <t>DomainResource.extension</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
-  </si>
-  <si>
-    <t>SupplyDelivery.extension:Transport</t>
-  </si>
-  <si>
-    <t>Transport</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/tdmi/StructureDefinition/dmi-transport}
-</t>
-  </si>
-  <si>
-    <t>DMI Transport</t>
-  </si>
-  <si>
-    <t>Extension créée dans ce volet pour représenter le transport.</t>
-  </si>
-  <si>
     <t>SupplyDelivery.extension:ReferenceOrganisationInterne</t>
   </si>
   <si>
@@ -533,9 +527,6 @@
     <t>.id</t>
   </si>
   <si>
-    <t>CX / EI (occasionally, more often EI maps to a resource id or a URL)</t>
-  </si>
-  <si>
     <t>SupplyDelivery.basedOn</t>
   </si>
   <si>
@@ -549,14 +540,7 @@
     <t>A plan, proposal or order that is fulfilled in whole or in part by this event.</t>
   </si>
   <si>
-    <t>References SHALL be a reference to an actual FHIR resource, and SHALL be resolveable (allowing for access control, temporary unavailability, etc.). Resolution can be either by retrieval from the URL, or, where applicable by resource type, by treating an absolute reference as a canonical URL and looking it up in a local registry/repository.</t>
-  </si>
-  <si>
     <t>Allows tracing of authorization for the event and tracking whether proposals/recommendations were acted upon.</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
   </si>
   <si>
     <t>Event.basedOn</t>
@@ -657,9 +641,6 @@
     <t>Indicates the type of dispensing event that is performed. Examples include: Trial Fill, Completion of Trial, Partial Fill, Emergency Fill, Samples, etc.</t>
   </si>
   <si>
-    <t>Not all terminology uses fit this general pattern. In some cases, models should not use CodeableConcept and use Coding directly and provide their own structure for managing text, codings, translations and the relationship between elements and pre- and post-coordination.</t>
-  </si>
-  <si>
     <t>The type of supply dispense.</t>
   </si>
   <si>
@@ -670,9 +651,6 @@
   </si>
   <si>
     <t>.code</t>
-  </si>
-  <si>
-    <t>CE/CNE/CWE</t>
   </si>
   <si>
     <t>SupplyDelivery.suppliedItem</t>
@@ -707,6 +685,9 @@
     <t>Element.id</t>
   </si>
   <si>
+    <t>n/a</t>
+  </si>
+  <si>
     <t>SupplyDelivery.suppliedItem.extension</t>
   </si>
   <si>
@@ -749,17 +730,7 @@
     <t>The amount of supply that has been dispensed. Includes unit of measure.</t>
   </si>
   <si>
-    <t>The context of use may frequently define what kind of quantity this is and therefore what kind of units can be used. The context of use may also restrict the values for the comparator.</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-qty-3:If a code for the unit is present, the system SHALL also be present {code.empty() or system.exists()}sqty-1:The comparator is not used on a SimpleQuantity {comparator.empty()}</t>
-  </si>
-  <si>
     <t>.quantity</t>
-  </si>
-  <si>
-    <t>SN (see also Range) or CQ</t>
   </si>
   <si>
     <t>SupplyDelivery.suppliedItem.item[x]</t>
@@ -1181,7 +1152,7 @@
     <col min="26" max="26" width="43.90234375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="30.5546875" customWidth="true" bestFit="true" hidden="true"/>
@@ -1190,7 +1161,7 @@
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="25.4609375" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="52.23046875" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="53.91015625" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="27.45703125" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="31.65234375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
@@ -1636,16 +1607,16 @@
         <v>87</v>
       </c>
       <c r="AI4" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ4" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ4" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK4" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL4" t="s" s="2">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="AM4" t="s" s="2">
         <v>77</v>
@@ -1656,10 +1627,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -1682,16 +1653,16 @@
         <v>88</v>
       </c>
       <c r="K5" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L5" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="M5" t="s" s="2">
         <v>103</v>
       </c>
-      <c r="L5" t="s" s="2">
+      <c r="N5" t="s" s="2">
         <v>104</v>
-      </c>
-      <c r="M5" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N5" t="s" s="2">
-        <v>106</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -1741,7 +1712,7 @@
         <v>77</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>78</v>
@@ -1750,16 +1721,16 @@
         <v>87</v>
       </c>
       <c r="AI5" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ5" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ5" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK5" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL5" t="s" s="2">
-        <v>108</v>
+        <v>77</v>
       </c>
       <c r="AM5" t="s" s="2">
         <v>77</v>
@@ -1770,10 +1741,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1796,16 +1767,16 @@
         <v>77</v>
       </c>
       <c r="K6" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L6" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="M6" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="N6" t="s" s="2">
         <v>110</v>
-      </c>
-      <c r="L6" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="M6" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="N6" t="s" s="2">
-        <v>113</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -1831,31 +1802,31 @@
         <v>77</v>
       </c>
       <c r="X6" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="Y6" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="Z6" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="AA6" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB6" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC6" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD6" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE6" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF6" t="s" s="2">
         <v>114</v>
-      </c>
-      <c r="Y6" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="Z6" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="AA6" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB6" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC6" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD6" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE6" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF6" t="s" s="2">
-        <v>117</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>78</v>
@@ -1864,16 +1835,16 @@
         <v>87</v>
       </c>
       <c r="AI6" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ6" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ6" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK6" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL6" t="s" s="2">
-        <v>108</v>
+        <v>77</v>
       </c>
       <c r="AM6" t="s" s="2">
         <v>77</v>
@@ -1884,14 +1855,14 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
@@ -1910,16 +1881,16 @@
         <v>77</v>
       </c>
       <c r="K7" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="L7" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="M7" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="N7" t="s" s="2">
         <v>120</v>
-      </c>
-      <c r="L7" t="s" s="2">
-        <v>121</v>
-      </c>
-      <c r="M7" t="s" s="2">
-        <v>122</v>
-      </c>
-      <c r="N7" t="s" s="2">
-        <v>123</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -1969,7 +1940,7 @@
         <v>77</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>78</v>
@@ -1978,16 +1949,16 @@
         <v>87</v>
       </c>
       <c r="AI7" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ7" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ7" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK7" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL7" t="s" s="2">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="AM7" t="s" s="2">
         <v>77</v>
@@ -1998,14 +1969,14 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
@@ -2024,16 +1995,16 @@
         <v>77</v>
       </c>
       <c r="K8" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="L8" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="M8" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="N8" t="s" s="2">
         <v>128</v>
-      </c>
-      <c r="L8" t="s" s="2">
-        <v>129</v>
-      </c>
-      <c r="M8" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="N8" t="s" s="2">
-        <v>131</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2083,7 +2054,7 @@
         <v>77</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>78</v>
@@ -2101,7 +2072,7 @@
         <v>77</v>
       </c>
       <c r="AL8" t="s" s="2">
-        <v>101</v>
+        <v>130</v>
       </c>
       <c r="AM8" t="s" s="2">
         <v>77</v>
@@ -2112,10 +2083,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -2138,13 +2109,13 @@
         <v>77</v>
       </c>
       <c r="K9" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="L9" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="M9" t="s" s="2">
         <v>134</v>
-      </c>
-      <c r="L9" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="M9" t="s" s="2">
-        <v>136</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -2183,19 +2154,17 @@
         <v>77</v>
       </c>
       <c r="AB9" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="AC9" s="2"/>
+      <c r="AD9" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE9" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="AF9" t="s" s="2">
         <v>137</v>
-      </c>
-      <c r="AC9" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="AD9" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE9" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="AF9" t="s" s="2">
-        <v>140</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>78</v>
@@ -2204,10 +2173,10 @@
         <v>79</v>
       </c>
       <c r="AI9" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>77</v>
@@ -2224,13 +2193,13 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="D10" t="s" s="2">
         <v>77</v>
@@ -2252,13 +2221,13 @@
         <v>77</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -2309,7 +2278,7 @@
         <v>77</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>78</v>
@@ -2318,10 +2287,10 @@
         <v>79</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>99</v>
+        <v>144</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>77</v>
@@ -2338,13 +2307,13 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C11" t="s" s="2">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D11" t="s" s="2">
         <v>77</v>
@@ -2366,13 +2335,13 @@
         <v>77</v>
       </c>
       <c r="K11" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="L11" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="M11" t="s" s="2">
         <v>149</v>
-      </c>
-      <c r="L11" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="M11" t="s" s="2">
-        <v>151</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -2423,7 +2392,7 @@
         <v>77</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>78</v>
@@ -2432,10 +2401,10 @@
         <v>79</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>99</v>
+        <v>144</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="AK11" t="s" s="2">
         <v>77</v>
@@ -2452,14 +2421,14 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
@@ -2478,19 +2447,19 @@
         <v>77</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="L12" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="M12" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="N12" t="s" s="2">
         <v>154</v>
       </c>
-      <c r="M12" t="s" s="2">
+      <c r="O12" t="s" s="2">
         <v>155</v>
-      </c>
-      <c r="N12" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="O12" t="s" s="2">
-        <v>157</v>
       </c>
       <c r="P12" t="s" s="2">
         <v>77</v>
@@ -2527,19 +2496,19 @@
         <v>77</v>
       </c>
       <c r="AB12" t="s" s="2">
-        <v>137</v>
+        <v>77</v>
       </c>
       <c r="AC12" t="s" s="2">
-        <v>138</v>
+        <v>77</v>
       </c>
       <c r="AD12" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE12" t="s" s="2">
-        <v>139</v>
+        <v>77</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>78</v>
@@ -2548,16 +2517,16 @@
         <v>79</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="AK12" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>101</v>
+        <v>130</v>
       </c>
       <c r="AM12" t="s" s="2">
         <v>77</v>
@@ -2568,10 +2537,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2594,16 +2563,16 @@
         <v>77</v>
       </c>
       <c r="K13" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="L13" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="M13" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="L13" t="s" s="2">
+      <c r="N13" t="s" s="2">
         <v>161</v>
-      </c>
-      <c r="M13" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>163</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -2653,7 +2622,7 @@
         <v>77</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>78</v>
@@ -2662,19 +2631,19 @@
         <v>79</v>
       </c>
       <c r="AI13" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ13" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ13" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK13" t="s" s="2">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>166</v>
+        <v>77</v>
       </c>
       <c r="AN13" t="s" s="2">
         <v>77</v>
@@ -2682,10 +2651,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2708,19 +2677,17 @@
         <v>88</v>
       </c>
       <c r="K14" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="L14" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="M14" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="N14" s="2"/>
+      <c r="O14" t="s" s="2">
         <v>168</v>
-      </c>
-      <c r="L14" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="M14" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="O14" t="s" s="2">
-        <v>172</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>77</v>
@@ -2769,7 +2736,7 @@
         <v>77</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>78</v>
@@ -2778,19 +2745,19 @@
         <v>79</v>
       </c>
       <c r="AI14" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ14" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ14" t="s" s="2">
-        <v>173</v>
-      </c>
       <c r="AK14" t="s" s="2">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="AN14" t="s" s="2">
         <v>77</v>
@@ -2798,10 +2765,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2824,19 +2791,19 @@
         <v>88</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="O15" t="s" s="2">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>77</v>
@@ -2885,7 +2852,7 @@
         <v>77</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>78</v>
@@ -2894,19 +2861,19 @@
         <v>79</v>
       </c>
       <c r="AI15" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ15" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ15" t="s" s="2">
-        <v>173</v>
-      </c>
       <c r="AK15" t="s" s="2">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="AN15" t="s" s="2">
         <v>77</v>
@@ -2914,10 +2881,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2940,16 +2907,16 @@
         <v>88</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -2975,13 +2942,13 @@
         <v>77</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>77</v>
@@ -2999,7 +2966,7 @@
         <v>77</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>78</v>
@@ -3008,16 +2975,16 @@
         <v>87</v>
       </c>
       <c r="AI16" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ16" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ16" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK16" t="s" s="2">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>77</v>
@@ -3028,10 +2995,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3054,17 +3021,15 @@
         <v>77</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>171</v>
-      </c>
+        <v>193</v>
+      </c>
+      <c r="N17" s="2"/>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>77</v>
@@ -3113,7 +3078,7 @@
         <v>77</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
@@ -3122,16 +3087,16 @@
         <v>87</v>
       </c>
       <c r="AI17" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ17" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ17" t="s" s="2">
-        <v>173</v>
-      </c>
       <c r="AK17" t="s" s="2">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>77</v>
@@ -3142,10 +3107,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3168,17 +3133,15 @@
         <v>77</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>205</v>
-      </c>
+        <v>199</v>
+      </c>
+      <c r="N18" s="2"/>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>77</v>
@@ -3203,13 +3166,13 @@
         <v>77</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>77</v>
@@ -3227,7 +3190,7 @@
         <v>77</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -3236,19 +3199,19 @@
         <v>87</v>
       </c>
       <c r="AI18" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ18" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ18" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK18" t="s" s="2">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>210</v>
+        <v>77</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>77</v>
@@ -3256,10 +3219,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3282,13 +3245,13 @@
         <v>77</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -3339,7 +3302,7 @@
         <v>77</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -3348,16 +3311,16 @@
         <v>87</v>
       </c>
       <c r="AI19" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ19" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ19" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK19" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>77</v>
@@ -3368,10 +3331,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3394,13 +3357,13 @@
         <v>77</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3451,7 +3414,7 @@
         <v>77</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
@@ -3469,7 +3432,7 @@
         <v>77</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>108</v>
+        <v>214</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>77</v>
@@ -3480,14 +3443,14 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -3506,16 +3469,16 @@
         <v>77</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -3553,19 +3516,19 @@
         <v>77</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>137</v>
+        <v>77</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>138</v>
+        <v>77</v>
       </c>
       <c r="AD21" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>139</v>
+        <v>77</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -3574,16 +3537,16 @@
         <v>79</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>101</v>
+        <v>214</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>77</v>
@@ -3594,14 +3557,14 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
@@ -3620,19 +3583,19 @@
         <v>88</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>77</v>
@@ -3681,7 +3644,7 @@
         <v>77</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -3690,16 +3653,16 @@
         <v>79</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>101</v>
+        <v>130</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>77</v>
@@ -3710,10 +3673,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3736,17 +3699,15 @@
         <v>77</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>234</v>
-      </c>
+        <v>227</v>
+      </c>
+      <c r="N23" s="2"/>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>77</v>
@@ -3795,7 +3756,7 @@
         <v>77</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -3804,19 +3765,19 @@
         <v>87</v>
       </c>
       <c r="AI23" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ23" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ23" t="s" s="2">
-        <v>235</v>
-      </c>
       <c r="AK23" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>237</v>
+        <v>77</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>77</v>
@@ -3824,10 +3785,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>238</v>
+        <v>229</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>238</v>
+        <v>229</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3850,13 +3811,13 @@
         <v>77</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>239</v>
+        <v>230</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>240</v>
+        <v>231</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3907,7 +3868,7 @@
         <v>77</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>238</v>
+        <v>229</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -3916,16 +3877,16 @@
         <v>87</v>
       </c>
       <c r="AI24" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ24" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ24" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK24" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>77</v>
@@ -3936,10 +3897,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>242</v>
+        <v>233</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>242</v>
+        <v>233</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3962,16 +3923,16 @@
         <v>88</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>246</v>
+        <v>237</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -4021,7 +3982,7 @@
         <v>77</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>242</v>
+        <v>233</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -4030,30 +3991,30 @@
         <v>87</v>
       </c>
       <c r="AI25" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ25" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ25" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK25" t="s" s="2">
-        <v>247</v>
+        <v>238</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>248</v>
+        <v>239</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>249</v>
+        <v>240</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>250</v>
+        <v>241</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>250</v>
+        <v>241</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4076,17 +4037,15 @@
         <v>77</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>251</v>
+        <v>242</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>252</v>
+        <v>243</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>171</v>
-      </c>
+        <v>244</v>
+      </c>
+      <c r="N26" s="2"/>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>77</v>
@@ -4135,7 +4094,7 @@
         <v>77</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>250</v>
+        <v>241</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -4144,16 +4103,16 @@
         <v>87</v>
       </c>
       <c r="AI26" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ26" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ26" t="s" s="2">
-        <v>173</v>
-      </c>
       <c r="AK26" t="s" s="2">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>255</v>
+        <v>246</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>77</v>
@@ -4164,10 +4123,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4190,17 +4149,15 @@
         <v>77</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>257</v>
+        <v>248</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>171</v>
-      </c>
+        <v>250</v>
+      </c>
+      <c r="N27" s="2"/>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>77</v>
@@ -4249,7 +4206,7 @@
         <v>77</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -4258,16 +4215,16 @@
         <v>87</v>
       </c>
       <c r="AI27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ27" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ27" t="s" s="2">
-        <v>173</v>
-      </c>
       <c r="AK27" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>77</v>
@@ -4278,10 +4235,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>261</v>
+        <v>252</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>261</v>
+        <v>252</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4304,17 +4261,15 @@
         <v>77</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>262</v>
+        <v>253</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>263</v>
+        <v>254</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>171</v>
-      </c>
+        <v>255</v>
+      </c>
+      <c r="N28" s="2"/>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>77</v>
@@ -4363,7 +4318,7 @@
         <v>77</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>261</v>
+        <v>252</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -4372,16 +4327,16 @@
         <v>79</v>
       </c>
       <c r="AI28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ28" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ28" t="s" s="2">
-        <v>173</v>
-      </c>
       <c r="AK28" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>265</v>
+        <v>256</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>77</v>

--- a/main/ig/StructureDefinition-dmi-supplydelivery-transport.xlsx
+++ b/main/ig/StructureDefinition-dmi-supplydelivery-transport.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-05T10:22:34+00:00</t>
+    <t>2026-03-05T10:23:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-dmi-supplydelivery-transport.xlsx
+++ b/main/ig/StructureDefinition-dmi-supplydelivery-transport.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1039" uniqueCount="257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1047" uniqueCount="266">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-05T10:23:55+00:00</t>
+    <t>2026-03-05T10:25:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -266,7 +266,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}</t>
+dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}</t>
   </si>
   <si>
     <t>Event</t>
@@ -316,10 +316,17 @@
     <t>Resource.meta</t>
   </si>
   <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
     <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
+    <t>N/A</t>
+  </si>
+  <si>
     <t>SupplyDelivery.implicitRules</t>
   </si>
   <si>
@@ -339,6 +346,9 @@
     <t>Resource.implicitRules</t>
   </si>
   <si>
+    <t>n/a</t>
+  </si>
+  <si>
     <t>SupplyDelivery.language</t>
   </si>
   <si>
@@ -416,9 +426,6 @@
     <t>DomainResource.contained</t>
   </si>
   <si>
-    <t>N/A</t>
-  </si>
-  <si>
     <t>SupplyDelivery.extension</t>
   </si>
   <si>
@@ -436,6 +443,9 @@
 </t>
   </si>
   <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
     <t>open</t>
   </si>
   <si>
@@ -462,10 +472,6 @@
     <t>Extension créée dans ce volet pour représenter le transport.</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
     <t>SupplyDelivery.extension:ReferenceOrganisationInterne</t>
   </si>
   <si>
@@ -527,6 +533,9 @@
     <t>.id</t>
   </si>
   <si>
+    <t>CX / EI (occasionally, more often EI maps to a resource id or a URL)</t>
+  </si>
+  <si>
     <t>SupplyDelivery.basedOn</t>
   </si>
   <si>
@@ -540,7 +549,14 @@
     <t>A plan, proposal or order that is fulfilled in whole or in part by this event.</t>
   </si>
   <si>
+    <t>References SHALL be a reference to an actual FHIR resource, and SHALL be resolveable (allowing for access control, temporary unavailability, etc.). Resolution can be either by retrieval from the URL, or, where applicable by resource type, by treating an absolute reference as a canonical URL and looking it up in a local registry/repository.</t>
+  </si>
+  <si>
     <t>Allows tracing of authorization for the event and tracking whether proposals/recommendations were acted upon.</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
   </si>
   <si>
     <t>Event.basedOn</t>
@@ -641,6 +657,9 @@
     <t>Indicates the type of dispensing event that is performed. Examples include: Trial Fill, Completion of Trial, Partial Fill, Emergency Fill, Samples, etc.</t>
   </si>
   <si>
+    <t>Not all terminology uses fit this general pattern. In some cases, models should not use CodeableConcept and use Coding directly and provide their own structure for managing text, codings, translations and the relationship between elements and pre- and post-coordination.</t>
+  </si>
+  <si>
     <t>The type of supply dispense.</t>
   </si>
   <si>
@@ -651,6 +670,9 @@
   </si>
   <si>
     <t>.code</t>
+  </si>
+  <si>
+    <t>CE/CNE/CWE</t>
   </si>
   <si>
     <t>SupplyDelivery.suppliedItem</t>
@@ -685,9 +707,6 @@
     <t>Element.id</t>
   </si>
   <si>
-    <t>n/a</t>
-  </si>
-  <si>
     <t>SupplyDelivery.suppliedItem.extension</t>
   </si>
   <si>
@@ -730,7 +749,17 @@
     <t>The amount of supply that has been dispensed. Includes unit of measure.</t>
   </si>
   <si>
+    <t>The context of use may frequently define what kind of quantity this is and therefore what kind of units can be used. The context of use may also restrict the values for the comparator.</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+qty-3:If a code for the unit is present, the system SHALL also be present {code.empty() or system.exists()}sqty-1:The comparator is not used on a SimpleQuantity {comparator.empty()}</t>
+  </si>
+  <si>
     <t>.quantity</t>
+  </si>
+  <si>
+    <t>SN (see also Range) or CQ</t>
   </si>
   <si>
     <t>SupplyDelivery.suppliedItem.item[x]</t>
@@ -1152,7 +1181,7 @@
     <col min="26" max="26" width="43.90234375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="30.5546875" customWidth="true" bestFit="true" hidden="true"/>
@@ -1161,7 +1190,7 @@
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="25.4609375" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="52.23046875" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="27.45703125" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="53.91015625" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="31.65234375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
@@ -1607,16 +1636,16 @@
         <v>87</v>
       </c>
       <c r="AI4" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL4" t="s" s="2">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="AM4" t="s" s="2">
         <v>77</v>
@@ -1627,10 +1656,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -1653,16 +1682,16 @@
         <v>88</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -1712,7 +1741,7 @@
         <v>77</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>78</v>
@@ -1721,16 +1750,16 @@
         <v>87</v>
       </c>
       <c r="AI5" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL5" t="s" s="2">
-        <v>77</v>
+        <v>108</v>
       </c>
       <c r="AM5" t="s" s="2">
         <v>77</v>
@@ -1741,10 +1770,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1767,16 +1796,16 @@
         <v>77</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -1802,13 +1831,13 @@
         <v>77</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>77</v>
@@ -1826,7 +1855,7 @@
         <v>77</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>78</v>
@@ -1835,16 +1864,16 @@
         <v>87</v>
       </c>
       <c r="AI6" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL6" t="s" s="2">
-        <v>77</v>
+        <v>108</v>
       </c>
       <c r="AM6" t="s" s="2">
         <v>77</v>
@@ -1855,14 +1884,14 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
@@ -1881,16 +1910,16 @@
         <v>77</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -1940,7 +1969,7 @@
         <v>77</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>78</v>
@@ -1949,16 +1978,16 @@
         <v>87</v>
       </c>
       <c r="AI7" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL7" t="s" s="2">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="AM7" t="s" s="2">
         <v>77</v>
@@ -1969,14 +1998,14 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
@@ -1995,16 +2024,16 @@
         <v>77</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2054,7 +2083,7 @@
         <v>77</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>78</v>
@@ -2072,7 +2101,7 @@
         <v>77</v>
       </c>
       <c r="AL8" t="s" s="2">
-        <v>130</v>
+        <v>101</v>
       </c>
       <c r="AM8" t="s" s="2">
         <v>77</v>
@@ -2083,10 +2112,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -2109,13 +2138,13 @@
         <v>77</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -2154,17 +2183,19 @@
         <v>77</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="AC9" s="2"/>
+        <v>137</v>
+      </c>
+      <c r="AC9" t="s" s="2">
+        <v>138</v>
+      </c>
       <c r="AD9" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>78</v>
@@ -2173,10 +2204,10 @@
         <v>79</v>
       </c>
       <c r="AI9" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>77</v>
@@ -2193,13 +2224,13 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="D10" t="s" s="2">
         <v>77</v>
@@ -2221,13 +2252,13 @@
         <v>77</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -2278,7 +2309,7 @@
         <v>77</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>78</v>
@@ -2287,10 +2318,10 @@
         <v>79</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>144</v>
+        <v>99</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>77</v>
@@ -2307,13 +2338,13 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C11" t="s" s="2">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D11" t="s" s="2">
         <v>77</v>
@@ -2335,13 +2366,13 @@
         <v>77</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -2392,7 +2423,7 @@
         <v>77</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>78</v>
@@ -2401,10 +2432,10 @@
         <v>79</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>144</v>
+        <v>99</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="AK11" t="s" s="2">
         <v>77</v>
@@ -2421,14 +2452,14 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
@@ -2447,19 +2478,19 @@
         <v>77</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="O12" t="s" s="2">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="P12" t="s" s="2">
         <v>77</v>
@@ -2496,19 +2527,19 @@
         <v>77</v>
       </c>
       <c r="AB12" t="s" s="2">
-        <v>77</v>
+        <v>137</v>
       </c>
       <c r="AC12" t="s" s="2">
-        <v>77</v>
+        <v>138</v>
       </c>
       <c r="AD12" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE12" t="s" s="2">
-        <v>77</v>
+        <v>139</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>78</v>
@@ -2517,16 +2548,16 @@
         <v>79</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="AK12" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>130</v>
+        <v>101</v>
       </c>
       <c r="AM12" t="s" s="2">
         <v>77</v>
@@ -2537,10 +2568,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2563,16 +2594,16 @@
         <v>77</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -2622,7 +2653,7 @@
         <v>77</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>78</v>
@@ -2631,19 +2662,19 @@
         <v>79</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>77</v>
+        <v>166</v>
       </c>
       <c r="AN13" t="s" s="2">
         <v>77</v>
@@ -2651,10 +2682,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2677,17 +2708,19 @@
         <v>88</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="N14" s="2"/>
+        <v>170</v>
+      </c>
+      <c r="N14" t="s" s="2">
+        <v>171</v>
+      </c>
       <c r="O14" t="s" s="2">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>77</v>
@@ -2736,7 +2769,7 @@
         <v>77</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>78</v>
@@ -2745,19 +2778,19 @@
         <v>79</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>99</v>
+        <v>173</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="AN14" t="s" s="2">
         <v>77</v>
@@ -2765,10 +2798,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2791,19 +2824,19 @@
         <v>88</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="O15" t="s" s="2">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>77</v>
@@ -2852,7 +2885,7 @@
         <v>77</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>78</v>
@@ -2861,19 +2894,19 @@
         <v>79</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>99</v>
+        <v>173</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="AN15" t="s" s="2">
         <v>77</v>
@@ -2881,10 +2914,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2907,16 +2940,16 @@
         <v>88</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -2942,31 +2975,31 @@
         <v>77</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="Y16" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="Z16" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="AA16" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB16" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC16" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD16" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE16" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF16" t="s" s="2">
         <v>186</v>
-      </c>
-      <c r="Z16" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="AA16" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB16" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC16" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD16" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE16" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF16" t="s" s="2">
-        <v>181</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>78</v>
@@ -2975,16 +3008,16 @@
         <v>87</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>77</v>
@@ -2995,10 +3028,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3021,15 +3054,17 @@
         <v>77</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="N17" s="2"/>
+        <v>198</v>
+      </c>
+      <c r="N17" t="s" s="2">
+        <v>171</v>
+      </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>77</v>
@@ -3078,7 +3113,7 @@
         <v>77</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
@@ -3087,16 +3122,16 @@
         <v>87</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>99</v>
+        <v>173</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>77</v>
@@ -3107,10 +3142,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3133,15 +3168,17 @@
         <v>77</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="N18" s="2"/>
+        <v>204</v>
+      </c>
+      <c r="N18" t="s" s="2">
+        <v>205</v>
+      </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>77</v>
@@ -3166,31 +3203,31 @@
         <v>77</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="Z18" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="AA18" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB18" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC18" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD18" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE18" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF18" t="s" s="2">
         <v>201</v>
-      </c>
-      <c r="AA18" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB18" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC18" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD18" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE18" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF18" t="s" s="2">
-        <v>196</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -3199,19 +3236,19 @@
         <v>87</v>
       </c>
       <c r="AI18" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>77</v>
+        <v>210</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>77</v>
@@ -3219,10 +3256,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3245,13 +3282,13 @@
         <v>77</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -3302,7 +3339,7 @@
         <v>77</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -3311,16 +3348,16 @@
         <v>87</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>77</v>
@@ -3331,10 +3368,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3357,13 +3394,13 @@
         <v>77</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3414,7 +3451,7 @@
         <v>77</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
@@ -3432,7 +3469,7 @@
         <v>77</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>214</v>
+        <v>108</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>77</v>
@@ -3443,14 +3480,14 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -3469,16 +3506,16 @@
         <v>77</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -3516,19 +3553,19 @@
         <v>77</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>77</v>
+        <v>137</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>77</v>
+        <v>138</v>
       </c>
       <c r="AD21" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>77</v>
+        <v>139</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -3537,16 +3574,16 @@
         <v>79</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>214</v>
+        <v>101</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>77</v>
@@ -3557,14 +3594,14 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
@@ -3583,19 +3620,19 @@
         <v>88</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>77</v>
@@ -3644,7 +3681,7 @@
         <v>77</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -3653,16 +3690,16 @@
         <v>79</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>130</v>
+        <v>101</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>77</v>
@@ -3673,10 +3710,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3699,15 +3736,17 @@
         <v>77</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="N23" s="2"/>
+        <v>233</v>
+      </c>
+      <c r="N23" t="s" s="2">
+        <v>234</v>
+      </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>77</v>
@@ -3756,7 +3795,7 @@
         <v>77</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -3765,19 +3804,19 @@
         <v>87</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>99</v>
+        <v>235</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>77</v>
+        <v>237</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>77</v>
@@ -3785,10 +3824,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>229</v>
+        <v>238</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>229</v>
+        <v>238</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3811,13 +3850,13 @@
         <v>77</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>230</v>
+        <v>239</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3868,7 +3907,7 @@
         <v>77</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>229</v>
+        <v>238</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -3877,16 +3916,16 @@
         <v>87</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>77</v>
@@ -3897,10 +3936,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3923,16 +3962,16 @@
         <v>88</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -3982,7 +4021,7 @@
         <v>77</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -3991,30 +4030,30 @@
         <v>87</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>238</v>
+        <v>247</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>240</v>
+        <v>249</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>241</v>
+        <v>250</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>241</v>
+        <v>250</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4037,15 +4076,17 @@
         <v>77</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>242</v>
+        <v>251</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>243</v>
+        <v>252</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="N26" s="2"/>
+        <v>253</v>
+      </c>
+      <c r="N26" t="s" s="2">
+        <v>171</v>
+      </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>77</v>
@@ -4094,7 +4135,7 @@
         <v>77</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>241</v>
+        <v>250</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -4103,16 +4144,16 @@
         <v>87</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>99</v>
+        <v>173</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>77</v>
@@ -4123,10 +4164,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4149,15 +4190,17 @@
         <v>77</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>249</v>
+        <v>258</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="N27" s="2"/>
+        <v>259</v>
+      </c>
+      <c r="N27" t="s" s="2">
+        <v>171</v>
+      </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>77</v>
@@ -4206,7 +4249,7 @@
         <v>77</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -4215,16 +4258,16 @@
         <v>87</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>99</v>
+        <v>173</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>251</v>
+        <v>260</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>77</v>
@@ -4235,10 +4278,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>252</v>
+        <v>261</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>252</v>
+        <v>261</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4261,15 +4304,17 @@
         <v>77</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>253</v>
+        <v>262</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>254</v>
+        <v>263</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="N28" s="2"/>
+        <v>264</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>171</v>
+      </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>77</v>
@@ -4318,7 +4363,7 @@
         <v>77</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>252</v>
+        <v>261</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -4327,16 +4372,16 @@
         <v>79</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>99</v>
+        <v>173</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>256</v>
+        <v>265</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>77</v>
